--- a/backups/DATA/2026/05/placement_backup_latest.xlsx
+++ b/backups/DATA/2026/05/placement_backup_latest.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="440">
   <si>
     <t>Sl No</t>
   </si>
@@ -115,7 +115,7 @@
     <t>2026-04-16 12:00:00</t>
   </si>
   <si>
-    <t>[{"name":"Full Name","type":"text","options":"","mandatory":"1"},{"name":"Phone No","type":"text","options":"","mandatory":"1"},{"name":"Alternate Phone No","type":"text","options":"","mandatory":"1"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"1"},{"name":"Hometown","type":"text","options":"","mandatory":"1"},{"name":"PAN No","type":"text","options":"","mandatory":"1"},{"name":"10th grade %","type":"text","options":"","mandatory":"1"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"1"},{"name":"UG Course Name","type":"text","options":"","mandatory":"1"},{"name":"UG %\/CGPA","type":"text","options":"","mandatory":"1"},{"name":"UG Year of Passing","type":"text","options":"","mandatory":"1"},{"name":"UG College Name","type":"text","options":"","mandatory":"1"},{"name":"Have you completed any internship?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Months of Internship","type":"text","options":"","mandatory":"1"},{"name":"Name of Organization","type":"text","options":"","mandatory":"1"},{"name":"Internship Role","type":"text","options":"","mandatory":"1"},{"name":"Certificate of Internship","type":"text","options":"","mandatory":"1"},{"name":"Are you available in person for interview?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"Are you ok with relocation?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"Are you ok with shifts?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"Willing to join Immediately ?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"Preferred Work Locations?","type":"text","options":"","mandatory":"1"},{"name":"Key Skills","type":"text","options":"","mandatory":"1"},{"name":"Upload Photo","type":"text","options":"","mandatory":"1"},{"name":"Upload Academic Certificates","type":"text","options":"","mandatory":"1"},{"name":"Upload ID Proof","type":"text","options":"","mandatory":"1"},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","type":"text","options":"I Agree","mandatory":"1"},{"name":"I hereby declare that the above information is correct.","type":"text","options":"I Agree","mandatory":"1"},{"name":"Declaration of Authenticity","type":"text","options":"I Agree","mandatory":"1"},{"name":"Agree to Terms and Conditions","type":"text","options":"I Agree","mandatory":"1"}]</t>
+    <t>{"enabled_fields":{"personal":["Full Name","Phone No","Email ID (please recheck the email before submitting)","City (Currently Residing In)"],"education":["12th grade\/PUC %","UG Degree","UG %\/CGPA"],"work":["Have you completed any internship?","Name of Organization","Internship Role"],"others":["Key Skills","Name of Certifications Completed","Certifications Upload","Upload Signature","I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","I hereby declare that the above information is correct.","Declaration of Authenticity","Agree to Terms and Conditions"]},"custom_fields":[]}</t>
   </si>
   <si>
     <t>2026</t>
@@ -346,315 +346,507 @@
     <t>Bluevine</t>
   </si>
   <si>
+    <t>[{"name":"10th grade %","type":"text","options":"","mandatory":"1"},{"name":"10th Board Name","type":"text","options":"","mandatory":"1"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"10th School Name","type":"text","options":"","mandatory":"1"},{"name":"10th School Location","type":"text","options":"","mandatory":"1"},{"name":"Full Name","type":"text","options":"","mandatory":"1"},{"name":"First Name","type":"text","options":"","mandatory":"1"},{"name":"Middle Name","type":"text","options":"","mandatory":"1"},{"name":"Last Name","type":"text","options":"","mandatory":"1"},{"name":"Phone No","type":"text","options":"","mandatory":"1"},{"name":"Alternate Phone No","type":"text","options":"","mandatory":"1"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"1"},{"name":"Alternate Email ID","type":"text","options":"","mandatory":"1"},{"name":"Gender","type":"text","options":"Male, Female, Other","mandatory":"1"},{"name":"DOB","type":"text","options":"","mandatory":"1"},{"name":"Current Address","type":"text","options":"","mandatory":"1"},{"name":"Permanent Address","type":"text","options":"","mandatory":"1"},{"name":"Aadhar No","type":"text","options":"","mandatory":"1"},{"name":"Blood Group","type":"text","options":"A+, A-, B+, B-, AB+, AB-, O+, O-","mandatory":"1"},{"name":"Emergency Contact Name","type":"text","options":"","mandatory":"1"},{"name":"Emergency Contact Number","type":"text","options":"","mandatory":"1"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"1"},{"name":"12th Board Name","type":"text","options":"","mandatory":"1"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC School Name","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC Location","type":"text","options":"","mandatory":"1"},{"name":"12th Stream","type":"text","options":"","mandatory":"1"}]</t>
+  </si>
+  <si>
+    <t>2026, 2027 , 2028</t>
+  </si>
+  <si>
+    <t>Ritu Srinivas</t>
+  </si>
+  <si>
+    <t>Research intern</t>
+  </si>
+  <si>
+    <t>Not provided</t>
+  </si>
+  <si>
+    <t>10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 AM - 6 PM </t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPIT Technologies </t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>https://www.kpit.com/</t>
+  </si>
+  <si>
+    <t>2026-05-04 12:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRBP </t>
+  </si>
+  <si>
+    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Communicative English_Psychology","BA-Political Science_Economics","BA-Psychology_Economics","BA-Psychology_English Literature","BA-Psychology_Journalism","BA-Psychology_Sociology","BA-Communication Studies","BA-Economics","BA-Journalism &amp; Mass Communication","BA-Psychology","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular"]</t>
+  </si>
+  <si>
+    <t>Rs. 5,50,000</t>
+  </si>
+  <si>
+    <t>Rs. 30,000</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNP Spark </t>
+  </si>
+  <si>
+    <t>2026-05-02 12:00:00</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"12th/PUC School Name","mandatory":true,"options":""},{"name":"12th/PUC Location","mandatory":true,"options":""},{"name":"12th Stream","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"UG College Name","mandatory":true,"options":""},{"name":"UG College Location","mandatory":true,"options":""},{"name":"UG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (UG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (UG)","mandatory":true,"options":""}]</t>
+  </si>
+  <si>
+    <t>Associate Accountant</t>
+  </si>
+  <si>
+    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BBA-Business Analytics","BBA-Regular"]</t>
+  </si>
+  <si>
+    <t>3 LPA - 3.5 LPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 AM - 5 PM </t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pentonix </t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>2026-01-09 12:00:00</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Passport No","mandatory":true,"options":""},{"name":"Nationality","mandatory":true,"options":""},{"name":"Category (General/OBC/SC/ST)","mandatory":true,"options":"General, OBC, SC, ST"},{"name":"Religion","mandatory":true,"options":"Hindu, Christian, Muslim, Sikh, Jain, Other"},{"name":"Blood Group","mandatory":true,"options":"A+, A-, B+, B-, AB+, AB-, O+, O-"},{"name":"Marital Status","mandatory":true,"options":"Single, Married, Divorced, Widowed"},{"name":"Father’s Name","mandatory":true,"options":""},{"name":"Mother’s Name","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"10th School Name","mandatory":true,"options":""},{"name":"10th School Location","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"Internship Project Details","mandatory":true,"options":""},{"name":"Internship Location","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""}]</t>
+  </si>
+  <si>
+    <t>2026, 2027,2028</t>
+  </si>
+  <si>
+    <t>Unnati</t>
+  </si>
+  <si>
+    <t>Visual Design Intern</t>
+  </si>
+  <si>
+    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Communicative English_Psychology","BA-History_Political Science","BA-History_Travel Tourism","BA-Political Science_Economics","BA-Political Science_Sociology","BA-Psychology_Economics","BA-Psychology_English Literature","BA-Psychology_Journalism","BA-Psychology_Sociology","BA-Travel &amp; Tourism_Journalism","BVoc-Hospitality and Tourism","BA-Communication Studies","BA-Economics","BA-Journalism &amp; Mass Communication","BA-Psychology","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","BSc-Biochemistry","BSc-Botany_Microbiology","BSc-Botany_Zoology","BSc-Chemistry_Biotechnology","BSc-Chemistry_Microbiology","BSc-COMPOSITE HOME SCIENCE","BSc-Computer Science_Mathematics","BSc-Economics_Statistics","BSc-Environmental Science &amp; Sustainability_Life Sciences","BSc-Mathematics_Physics","BSc-Microbiology_Zoology","BSc-Nutrition &amp; Dietetics_Human Development","BSc-Zoology_Biotechnology","BSc-Biotechnology","BSc-Data Science","BSc-Fashion and Apparel Design","BSc-Food Science &amp; Nutrition","BSc-Interior Design &amp; Management","Bachelor of Computer Applications","MCom-Financial Analysis","MCom-General","MCom-International Business","One Year Masters Degree In Commerce","MA-Economics","MA-English","MA-Public Policy","PG Diploma in Business Applications","PG Diploma in Business Intelligence and Analytics","Master of Business Administration","PG Diploma in Management Analytics","MSc-Biochemistry","MSc-Biotechnology","MSc-Botany","MSc-Chemistry","MSc-Computer Science (Data Science Specialization)","MSc-Electronics","MSc-Food Science &amp; Nutrition","MSc-Life Science","MSc-Mathematics","MSc-Psychology","MSc-Human Development","Master of Computer Applications","All UG","All PG"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flexible </t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Aura illumination</t>
+  </si>
+  <si>
+    <t>2026-03-12 12:00:00</t>
+  </si>
+  <si>
+    <t>{"enabled_fields":{"personal":["Full Name","First Name","Middle Name","Last Name","Phone No","Alternate Phone No","Email ID (please recheck the email before submitting)","Alternate Email ID","Gender","DOB","Hometown","State","District","City (Currently Residing In)","Pincode","Current Address","Permanent Address","PAN No","Aadhar No","Passport No","Nationality","Category (General\/OBC\/SC\/ST)","Religion","Blood Group","Marital Status","Father's Name","Mother's Name","Emergency Contact Name","Emergency Contact Number"],"education":["10th grade %","10th Board Name","10th Year Of Passing","10th School Name","10th School Location","12th grade\/PUC %","12th Board Name","12th Year Of Passing","12th\/PUC School Name","12th\/PUC Location","12th Stream","Diploma %","Diploma Year Of Passing","Diploma Specialization","Diploma College Name","Diploma University Name","UG Degree","UG Course Name","UG %\/CGPA","UG Year of Passing","UG Stream\/Specialization","UG College Name","UG College Location","UG University Name","Active Backlogs (UG)?","No. of Backlogs (UG)","PG Degree","PG Course Name","PG %\/CGPA","PG Year of Passing","PG Stream\/Specialization","PG College Name","PG College Location","PG University Name","Active Backlogs (PG)?","No. of Backlogs (PG)"],"work":["Have you completed any internship?","No. of Months of Internship","Name of Organization","Internship Role","Internship Project Details","Internship Location","Certificate of Internship","Have Prior Full-time Experience?","Company Name","Designation","Duration (Months)","Job Role Description","Last Drawn Salary (If any)","Reason for Leaving (If any)","Project Title","Project Description","Technologies Used","GitHub\/Project URL","Upload Portfolio","Upload Cover Letter","LinkedIn Profile","Dribbble\/Behance Link","Are you available in person for interview?","Are you ok with relocation?","Are you ok with shifts?","Willing to join Immediately ?","Preferred Work Locations?","Preferred Industry","Preferred Job Role"],"others":["Certifications Upload","Technical Skills","Programming Languages Known","Languages Known (Read\/Write\/Speak)","Upload Photo","Upload Academic Certificates","Upload ID Proof","Upload Signature","Additional Documents (You can upload multiple files Ex: Project, Portfolio)","I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","I hereby declare that the above information is correct.","Declaration of Authenticity","Agree to Terms and Conditions"]},"custom_fields":[]}</t>
+  </si>
+  <si>
+    <t>2026, 2027, 2028</t>
+  </si>
+  <si>
+    <t>Shantinagar</t>
+  </si>
+  <si>
+    <t>Human Resource Intern</t>
+  </si>
+  <si>
+    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","MCom-Financial Analysis","MCom-General","MCom-International Business","One Year Masters Degree In Commerce","Master of Business Administration"]</t>
+  </si>
+  <si>
+    <t>Flexible</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>India Hemp Organics</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>https://indiahemporganics.com/</t>
+  </si>
+  <si>
+    <t>2026-05-03</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","type":"text","options":"","mandatory":"0"},{"name":"Phone No","type":"text","options":"","mandatory":"0"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"0"},{"name":"Gender","type":"text","options":"","mandatory":"0"},{"name":"10th grade %","type":"text","options":"","mandatory":"0"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":"0"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"0"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":"0"}]</t>
+  </si>
+  <si>
+    <t>Manasi</t>
+  </si>
+  <si>
+    <t>Business Development intern</t>
+  </si>
+  <si>
+    <t>7000-10000</t>
+  </si>
+  <si>
+    <t>1pm - 7pm</t>
+  </si>
+  <si>
+    <t>Healthcare &amp; Wellness</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akshara Enterprise </t>
+  </si>
+  <si>
+    <t>2026-05-01 11:00:00</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"PG Degree","mandatory":false,"options":""},{"name":"PG Course Name","mandatory":false,"options":""},{"name":"PG %/CGPA","mandatory":false,"options":""},{"name":"PG Year of Passing","mandatory":false,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""}]</t>
+  </si>
+  <si>
+    <t>Jagriti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR </t>
+  </si>
+  <si>
+    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Communicative English_Psychology","BA-Psychology_Economics","BA-Psychology_English Literature","BA-Psychology_Journalism","BA-Psychology_Sociology","BA-Psychology","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","MCom-Financial Analysis","MCom-General","MCom-International Business","One Year Masters Degree In Commerce","PG Diploma in Business Applications","PG Diploma in Business Intelligence and Analytics","Master of Business Administration","PG Diploma in Management Analytics"]</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>9:30 AM - 7 PM</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Deloitte</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Passport No","mandatory":true,"options":""},{"name":"Nationality","mandatory":true,"options":""},{"name":"Category (General/OBC/SC/ST)","mandatory":true,"options":"General, OBC, SC, ST"},{"name":"Religion","mandatory":true,"options":"Hindu, Christian, Muslim, Sikh, Jain, Other"},{"name":"Blood Group","mandatory":true,"options":"A+, A-, B+, B-, AB+, AB-, O+, O-"},{"name":"Marital Status","mandatory":true,"options":"Single, Married, Divorced, Widowed"},{"name":"Father’s Name","mandatory":true,"options":""},{"name":"Mother’s Name","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"Internship Project Details","mandatory":true,"options":""},{"name":"Internship Location","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"10th School Name","mandatory":true,"options":""},{"name":"10th School Location","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"12th/PUC School Name","mandatory":true,"options":""},{"name":"12th/PUC Location","mandatory":true,"options":""},{"name":"12th Stream","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"UG College Name","mandatory":true,"options":""},{"name":"UG College Location","mandatory":true,"options":""},{"name":"UG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (UG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (UG)","mandatory":true,"options":""},{"name":"PG Degree","mandatory":true,"options":""},{"name":"PG Course Name","mandatory":true,"options":""},{"name":"PG %/CGPA","mandatory":true,"options":""},{"name":"PG Year of Passing","mandatory":true,"options":""},{"name":"PG Stream/Specialization","mandatory":true,"options":""},{"name":"PG College Name","mandatory":true,"options":""},{"name":"PG College Location","mandatory":true,"options":""},{"name":"PG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (PG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (PG)","mandatory":true,"options":""},{"name":"Have Prior Full-time Experience?","mandatory":true,"options":"Yes, No"},{"name":"Company Name","mandatory":true,"options":""},{"name":"Designation","mandatory":true,"options":""},{"name":"Duration (Months)","mandatory":true,"options":""},{"name":"Job Role Description","mandatory":true,"options":""},{"name":"Last Drawn Salary (If any)","mandatory":true,"options":""},{"name":"Reason for Leaving (If any)","mandatory":true,"options":""},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","mandatory":true,"options":"I Agree"},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"},{"name":"Declaration of Authenticity","mandatory":true,"options":"I Agree"},{"name":"Agree to Terms and Conditions","mandatory":true,"options":"I Agree"}]</t>
+  </si>
+  <si>
+    <t>2026, 2027</t>
+  </si>
+  <si>
+    <t>Devnanda</t>
+  </si>
+  <si>
+    <t>Software engineer</t>
+  </si>
+  <si>
+    <t>["BSc-Biochemistry","BSc-Botany_Microbiology","BSc-Botany_Zoology","BSc-Chemistry_Biotechnology","BSc-Chemistry_Microbiology","BSc-COMPOSITE HOME SCIENCE","BSc-Computer Science_Mathematics","BSc-Economics_Statistics","BSc-Environmental Science &amp; Sustainability_Life Sciences","BSc-Mathematics_Physics","BSc-Microbiology_Zoology","BSc-Nutrition &amp; Dietetics_Human Development","BSc-Zoology_Biotechnology","BSc-Biotechnology","BSc-Data Science","BSc-Fashion and Apparel Design","BSc-Food Science &amp; Nutrition","BSc-Interior Design &amp; Management","Bachelor of Computer Applications","MSc-Biochemistry","MSc-Biotechnology","MSc-Botany","MSc-Chemistry","MSc-Computer Science (Data Science Specialization)","MSc-Electronics","MSc-Food Science &amp; Nutrition","MSc-Life Science","MSc-Mathematics","MSc-Psychology","MSc-Human Development","Master of Computer Applications"]</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>800000</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>PwC</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","type":"text","options":"","mandatory":"1"},{"name":"First Name","type":"text","options":"","mandatory":"1"},{"name":"Middle Name","type":"text","options":"","mandatory":"1"},{"name":"Last Name","type":"text","options":"","mandatory":"1"},{"name":"Phone No","type":"text","options":"","mandatory":"1"},{"name":"Alternate Phone No","type":"text","options":"","mandatory":"1"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"1"},{"name":"Alternate Email ID","type":"text","options":"","mandatory":"1"},{"name":"Gender","type":"text","options":"Male, Female, Other","mandatory":"1"},{"name":"DOB","type":"text","options":"","mandatory":"1"},{"name":"Hometown","type":"text","options":"","mandatory":"1"},{"name":"State","type":"text","options":"","mandatory":"1"},{"name":"District","type":"text","options":"","mandatory":"1"},{"name":"City (Currently Residing In)","type":"text","options":"","mandatory":"1"},{"name":"Pincode","type":"text","options":"","mandatory":"1"},{"name":"Current Address","type":"text","options":"","mandatory":"1"},{"name":"Permanent Address","type":"text","options":"","mandatory":"1"},{"name":"PAN No","type":"text","options":"","mandatory":"1"},{"name":"Aadhar No","type":"text","options":"","mandatory":"1"},{"name":"Passport No","type":"text","options":"","mandatory":"1"},{"name":"Nationality","type":"text","options":"","mandatory":"1"},{"name":"Category (General\/OBC\/SC\/ST)","type":"text","options":"General, OBC, SC, ST","mandatory":"1"},{"name":"Religion","type":"text","options":"Hindu, Christian, Muslim, Sikh, Jain, Other","mandatory":"1"},{"name":"Blood Group","type":"text","options":"A+, A-, B+, B-, AB+, AB-, O+, O-","mandatory":"1"},{"name":"Marital Status","type":"text","options":"Single, Married, Divorced, Widowed","mandatory":"1"},{"name":"Father\u2019s Name","type":"text","options":"","mandatory":"1"},{"name":"Mother\u2019s Name","type":"text","options":"","mandatory":"1"},{"name":"Emergency Contact Name","type":"text","options":"","mandatory":"1"},{"name":"Emergency Contact Number","type":"text","options":"","mandatory":"1"},{"name":"10th grade %","type":"text","options":"","mandatory":"1"},{"name":"10th Board Name","type":"text","options":"","mandatory":"1"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"10th School Name","type":"text","options":"","mandatory":"1"},{"name":"10th School Location","type":"text","options":"","mandatory":"1"},{"name":"UG Degree","type":"text","options":"","mandatory":"1"},{"name":"UG Course Name","type":"text","options":"","mandatory":"1"},{"name":"UG %\/CGPA","type":"text","options":"","mandatory":"1"},{"name":"UG Year of Passing","type":"text","options":"","mandatory":"1"},{"name":"UG Stream\/Specialization","type":"text","options":"","mandatory":"1"},{"name":"UG College Name","type":"text","options":"","mandatory":"1"},{"name":"UG College Location","type":"text","options":"","mandatory":"1"},{"name":"UG University Name","type":"text","options":"","mandatory":"1"},{"name":"Active Backlogs (UG)?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Backlogs (UG)","type":"text","options":"","mandatory":"1"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"1"},{"name":"12th Board Name","type":"text","options":"","mandatory":"1"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC School Name","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC Location","type":"text","options":"","mandatory":"1"},{"name":"12th Stream","type":"text","options":"","mandatory":"1"},{"name":"PG Degree","type":"text","options":"","mandatory":"1"},{"name":"PG Course Name","type":"text","options":"","mandatory":"1"},{"name":"PG %\/CGPA","type":"text","options":"","mandatory":"1"},{"name":"PG Year of Passing","type":"text","options":"","mandatory":"1"},{"name":"PG Stream\/Specialization","type":"text","options":"","mandatory":"1"},{"name":"PG College Name","type":"text","options":"","mandatory":"1"},{"name":"PG College Location","type":"text","options":"","mandatory":"1"},{"name":"PG University Name","type":"text","options":"","mandatory":"1"},{"name":"Active Backlogs (PG)?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Backlogs (PG)","type":"text","options":"","mandatory":"1"},{"name":"Have you completed any internship?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Months of Internship","type":"text","options":"","mandatory":"1"},{"name":"Name of Organization","type":"text","options":"","mandatory":"1"},{"name":"Internship Role","type":"text","options":"","mandatory":"1"},{"name":"Internship Project Details","type":"text","options":"","mandatory":"1"},{"name":"Internship Location","type":"text","options":"","mandatory":"1"},{"name":"Certificate of Internship","type":"text","options":"","mandatory":"1"},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","type":"text","options":"I Agree","mandatory":"1"},{"name":"I hereby declare that the above information is correct.","type":"text","options":"I Agree","mandatory":"1"},{"name":"Declaration of Authenticity","type":"text","options":"I Agree","mandatory":"1"},{"name":"Agree to Terms and Conditions","type":"text","options":"I Agree","mandatory":"1"}]</t>
+  </si>
+  <si>
+    <t>2025, 2026, 2027, 2028</t>
+  </si>
+  <si>
+    <t>2028-2029</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>9:30AM-6:30PM</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>D E Shaw</t>
+  </si>
+  <si>
+    <t>Global investment &amp; Technology</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"Certificate of Internship","mandatory":true,"options":""},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","mandatory":true,"options":"I Agree"},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"},{"name":"Declaration of Authenticity","mandatory":true,"options":"I Agree"},{"name":"Agree to Terms and Conditions","mandatory":true,"options":"I Agree"}]</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Intern </t>
+  </si>
+  <si>
+    <t>900000</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>9:00AM- 6:00 PM</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Morgan Stanley</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"}]</t>
+  </si>
+  <si>
+    <t>madiha</t>
+  </si>
+  <si>
+    <t>Analyst Trainee</t>
+  </si>
+  <si>
+    <t>60,000</t>
+  </si>
+  <si>
+    <t>Apprenticeship (Part Time)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>KPMG India</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","type":"text","options":"","mandatory":1,"section":"personal"},{"name":"10th grade %","type":"text","options":"","mandatory":1,"section":"education"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":1,"section":"education"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":1,"section":"education"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":1,"section":"education"},{"name":"PG Degree","type":"text","options":"","mandatory":0,"section":"education"},{"name":"PG Year of Passing","type":"text","options":"","mandatory":0,"section":"education"},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","type":"text","options":"","mandatory":0,"section":"others"},{"name":"I hereby declare that the above information is correct.","type":"text","options":"","mandatory":0,"section":"others"},{"name":"Languages","type":"text","options":"","mandatory":0,"section":"others"}]</t>
+  </si>
+  <si>
+    <t>Madiha</t>
+  </si>
+  <si>
+    <t>ESG Intern</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>Drive 2</t>
   </si>
   <si>
-    <t>[{"name":"10th grade %","type":"text","options":"","mandatory":"1"},{"name":"10th Board Name","type":"text","options":"","mandatory":"1"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"10th School Name","type":"text","options":"","mandatory":"1"},{"name":"10th School Location","type":"text","options":"","mandatory":"1"},{"name":"Full Name","type":"text","options":"","mandatory":"1"},{"name":"First Name","type":"text","options":"","mandatory":"1"},{"name":"Middle Name","type":"text","options":"","mandatory":"1"},{"name":"Last Name","type":"text","options":"","mandatory":"1"},{"name":"Phone No","type":"text","options":"","mandatory":"1"},{"name":"Alternate Phone No","type":"text","options":"","mandatory":"1"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"1"},{"name":"Alternate Email ID","type":"text","options":"","mandatory":"1"},{"name":"Gender","type":"text","options":"Male, Female, Other","mandatory":"1"},{"name":"DOB","type":"text","options":"","mandatory":"1"},{"name":"Current Address","type":"text","options":"","mandatory":"1"},{"name":"Permanent Address","type":"text","options":"","mandatory":"1"},{"name":"Aadhar No","type":"text","options":"","mandatory":"1"},{"name":"Blood Group","type":"text","options":"A+, A-, B+, B-, AB+, AB-, O+, O-","mandatory":"1"},{"name":"Emergency Contact Name","type":"text","options":"","mandatory":"1"},{"name":"Emergency Contact Number","type":"text","options":"","mandatory":"1"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"1"},{"name":"12th Board Name","type":"text","options":"","mandatory":"1"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC School Name","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC Location","type":"text","options":"","mandatory":"1"},{"name":"12th Stream","type":"text","options":"","mandatory":"1"}]</t>
-  </si>
-  <si>
-    <t>2026, 2027 , 2028</t>
-  </si>
-  <si>
-    <t>Ritu Srinivas</t>
-  </si>
-  <si>
-    <t>Research intern</t>
-  </si>
-  <si>
-    <t>Not provided</t>
-  </si>
-  <si>
-    <t>10,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 AM - 6 PM </t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPIT Technologies </t>
-  </si>
-  <si>
-    <t>Human Resources</t>
-  </si>
-  <si>
-    <t>https://www.kpit.com/</t>
-  </si>
-  <si>
-    <t>2026-05-04 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRBP </t>
-  </si>
-  <si>
-    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Communicative English_Psychology","BA-Political Science_Economics","BA-Psychology_Economics","BA-Psychology_English Literature","BA-Psychology_Journalism","BA-Psychology_Sociology","BA-Communication Studies","BA-Economics","BA-Journalism &amp; Mass Communication","BA-Psychology","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular"]</t>
-  </si>
-  <si>
-    <t>Rs. 5,50,000</t>
-  </si>
-  <si>
-    <t>Rs. 30,000</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNP Spark </t>
-  </si>
-  <si>
-    <t>2026-05-02 12:00:00</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"12th/PUC School Name","mandatory":true,"options":""},{"name":"12th/PUC Location","mandatory":true,"options":""},{"name":"12th Stream","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"UG College Name","mandatory":true,"options":""},{"name":"UG College Location","mandatory":true,"options":""},{"name":"UG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (UG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (UG)","mandatory":true,"options":""}]</t>
-  </si>
-  <si>
-    <t>Associate Accountant</t>
-  </si>
-  <si>
-    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BBA-Business Analytics","BBA-Regular"]</t>
-  </si>
-  <si>
-    <t>3 LPA - 3.5 LPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 AM - 5 PM </t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pentonix </t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>2026-01-09 12:00:00</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Passport No","mandatory":true,"options":""},{"name":"Nationality","mandatory":true,"options":""},{"name":"Category (General/OBC/SC/ST)","mandatory":true,"options":"General, OBC, SC, ST"},{"name":"Religion","mandatory":true,"options":"Hindu, Christian, Muslim, Sikh, Jain, Other"},{"name":"Blood Group","mandatory":true,"options":"A+, A-, B+, B-, AB+, AB-, O+, O-"},{"name":"Marital Status","mandatory":true,"options":"Single, Married, Divorced, Widowed"},{"name":"Father’s Name","mandatory":true,"options":""},{"name":"Mother’s Name","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"10th School Name","mandatory":true,"options":""},{"name":"10th School Location","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"Internship Project Details","mandatory":true,"options":""},{"name":"Internship Location","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""}]</t>
-  </si>
-  <si>
-    <t>2026, 2027,2028</t>
-  </si>
-  <si>
-    <t>Unnati</t>
-  </si>
-  <si>
-    <t>Visual Design Intern</t>
-  </si>
-  <si>
-    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Communicative English_Psychology","BA-History_Political Science","BA-History_Travel Tourism","BA-Political Science_Economics","BA-Political Science_Sociology","BA-Psychology_Economics","BA-Psychology_English Literature","BA-Psychology_Journalism","BA-Psychology_Sociology","BA-Travel &amp; Tourism_Journalism","BVoc-Hospitality and Tourism","BA-Communication Studies","BA-Economics","BA-Journalism &amp; Mass Communication","BA-Psychology","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","BSc-Biochemistry","BSc-Botany_Microbiology","BSc-Botany_Zoology","BSc-Chemistry_Biotechnology","BSc-Chemistry_Microbiology","BSc-COMPOSITE HOME SCIENCE","BSc-Computer Science_Mathematics","BSc-Economics_Statistics","BSc-Environmental Science &amp; Sustainability_Life Sciences","BSc-Mathematics_Physics","BSc-Microbiology_Zoology","BSc-Nutrition &amp; Dietetics_Human Development","BSc-Zoology_Biotechnology","BSc-Biotechnology","BSc-Data Science","BSc-Fashion and Apparel Design","BSc-Food Science &amp; Nutrition","BSc-Interior Design &amp; Management","Bachelor of Computer Applications","MCom-Financial Analysis","MCom-General","MCom-International Business","One Year Masters Degree In Commerce","MA-Economics","MA-English","MA-Public Policy","PG Diploma in Business Applications","PG Diploma in Business Intelligence and Analytics","Master of Business Administration","PG Diploma in Management Analytics","MSc-Biochemistry","MSc-Biotechnology","MSc-Botany","MSc-Chemistry","MSc-Computer Science (Data Science Specialization)","MSc-Electronics","MSc-Food Science &amp; Nutrition","MSc-Life Science","MSc-Mathematics","MSc-Psychology","MSc-Human Development","Master of Computer Applications","All UG","All PG"]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flexible </t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Aura illumination</t>
-  </si>
-  <si>
-    <t>2026-03-12 12:00:00</t>
-  </si>
-  <si>
-    <t>2026, 2027, 2028</t>
-  </si>
-  <si>
-    <t>Shantinagar</t>
-  </si>
-  <si>
-    <t>Human Resource Intern</t>
-  </si>
-  <si>
-    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","MCom-Financial Analysis","MCom-General","MCom-International Business","One Year Masters Degree In Commerce","Master of Business Administration"]</t>
-  </si>
-  <si>
-    <t>Flexible</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>India Hemp Organics</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>https://indiahemporganics.com/</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Passport No","mandatory":true,"options":""},{"name":"Nationality","mandatory":true,"options":""},{"name":"Category (General/OBC/SC/ST)","mandatory":true,"options":"General, OBC, SC, ST"},{"name":"Religion","mandatory":true,"options":"Hindu, Christian, Muslim, Sikh, Jain, Other"},{"name":"Blood Group","mandatory":true,"options":"A+, A-, B+, B-, AB+, AB-, O+, O-"},{"name":"Marital Status","mandatory":true,"options":"Single, Married, Divorced, Widowed"},{"name":"Father’s Name","mandatory":true,"options":""},{"name":"Mother’s Name","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"10th School Name","mandatory":true,"options":""},{"name":"10th School Location","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"12th/PUC School Name","mandatory":true,"options":""},{"name":"12th/PUC Location","mandatory":true,"options":""},{"name":"12th Stream","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"UG College Name","mandatory":true,"options":""},{"name":"UG College Location","mandatory":true,"options":""},{"name":"UG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (UG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (UG)","mandatory":true,"options":""},{"name":"Diploma %","mandatory":true,"options":""},{"name":"Diploma Year Of Passing","mandatory":true,"options":""},{"name":"Diploma Specialization","mandatory":true,"options":""},{"name":"Diploma College Name","mandatory":true,"options":""},{"name":"Diploma University Name","mandatory":true,"options":""},{"name":"PG Degree","mandatory":true,"options":""},{"name":"PG Course Name","mandatory":true,"options":""},{"name":"PG %/CGPA","mandatory":true,"options":""},{"name":"PG Year of Passing","mandatory":true,"options":""},{"name":"PG Stream/Specialization","mandatory":true,"options":""},{"name":"PG College Name","mandatory":true,"options":""},{"name":"PG College Location","mandatory":true,"options":""},{"name":"PG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (PG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (PG)","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"Internship Project Details","mandatory":true,"options":""},{"name":"Internship Location","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""},{"name":"Key Skills","mandatory":true,"options":""},{"name":"Name of Certifications Completed","mandatory":true,"options":""},{"name":"Certifications Upload","mandatory":true,"options":""},{"name":"Technical Skills","mandatory":true,"options":""},{"name":"Programming Languages Known","mandatory":true,"options":""},{"name":"Languages Known (Read/Write/Speak)","mandatory":true,"options":"English, Hindi, Kannada, Tamil, Telugu, Malayalam, Others"},{"name":"Upload Photo","mandatory":true,"options":""},{"name":"Upload Academic Certificates","mandatory":true,"options":""},{"name":"Upload ID Proof","mandatory":true,"options":""},{"name":"Upload Signature","mandatory":true,"options":""},{"name":"Additional Documents (You can upload multiple files Ex: Project, Portfolio)","mandatory":true,"options":""},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","mandatory":true,"options":"I Agree"},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"},{"name":"Declaration of Authenticity","mandatory":true,"options":"I Agree"},{"name":"Agree to Terms and Conditions","mandatory":true,"options":"I Agree"}]</t>
-  </si>
-  <si>
-    <t>Manasi</t>
-  </si>
-  <si>
-    <t>Business Development intern</t>
-  </si>
-  <si>
-    <t>7000-10000</t>
-  </si>
-  <si>
-    <t>1pm - 7pm</t>
-  </si>
-  <si>
-    <t>Healthcare &amp; Wellness</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akshara Enterprise </t>
-  </si>
-  <si>
-    <t>2026-05-01 11:00:00</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"PG Degree","mandatory":false,"options":""},{"name":"PG Course Name","mandatory":false,"options":""},{"name":"PG %/CGPA","mandatory":false,"options":""},{"name":"PG Year of Passing","mandatory":false,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""}]</t>
-  </si>
-  <si>
-    <t>Jagriti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR </t>
-  </si>
-  <si>
-    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Communicative English_Psychology","BA-Psychology_Economics","BA-Psychology_English Literature","BA-Psychology_Journalism","BA-Psychology_Sociology","BA-Psychology","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","MCom-Financial Analysis","MCom-General","MCom-International Business","One Year Masters Degree In Commerce","PG Diploma in Business Applications","PG Diploma in Business Intelligence and Analytics","Master of Business Administration","PG Diploma in Management Analytics"]</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>9:30 AM - 7 PM</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Deloitte</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"First Name","mandatory":true,"options":""},{"name":"Middle Name","mandatory":true,"options":""},{"name":"Last Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"Gender","mandatory":true,"options":"Male, Female, Other"},{"name":"DOB","mandatory":true,"options":""},{"name":"Hometown","mandatory":true,"options":""},{"name":"State","mandatory":true,"options":""},{"name":"District","mandatory":true,"options":""},{"name":"City (Currently Residing In)","mandatory":true,"options":""},{"name":"Pincode","mandatory":true,"options":""},{"name":"Current Address","mandatory":true,"options":""},{"name":"Permanent Address","mandatory":true,"options":""},{"name":"PAN No","mandatory":true,"options":""},{"name":"Aadhar No","mandatory":true,"options":""},{"name":"Passport No","mandatory":true,"options":""},{"name":"Nationality","mandatory":true,"options":""},{"name":"Category (General/OBC/SC/ST)","mandatory":true,"options":"General, OBC, SC, ST"},{"name":"Religion","mandatory":true,"options":"Hindu, Christian, Muslim, Sikh, Jain, Other"},{"name":"Blood Group","mandatory":true,"options":"A+, A-, B+, B-, AB+, AB-, O+, O-"},{"name":"Marital Status","mandatory":true,"options":"Single, Married, Divorced, Widowed"},{"name":"Father’s Name","mandatory":true,"options":""},{"name":"Mother’s Name","mandatory":true,"options":""},{"name":"Emergency Contact Name","mandatory":true,"options":""},{"name":"Emergency Contact Number","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"No. of Months of Internship","mandatory":true,"options":""},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"Internship Project Details","mandatory":true,"options":""},{"name":"Internship Location","mandatory":true,"options":""},{"name":"Certificate of Internship","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"10th School Name","mandatory":true,"options":""},{"name":"10th School Location","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"12th/PUC School Name","mandatory":true,"options":""},{"name":"12th/PUC Location","mandatory":true,"options":""},{"name":"12th Stream","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"UG Stream/Specialization","mandatory":true,"options":""},{"name":"UG College Name","mandatory":true,"options":""},{"name":"UG College Location","mandatory":true,"options":""},{"name":"UG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (UG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (UG)","mandatory":true,"options":""},{"name":"PG Degree","mandatory":true,"options":""},{"name":"PG Course Name","mandatory":true,"options":""},{"name":"PG %/CGPA","mandatory":true,"options":""},{"name":"PG Year of Passing","mandatory":true,"options":""},{"name":"PG Stream/Specialization","mandatory":true,"options":""},{"name":"PG College Name","mandatory":true,"options":""},{"name":"PG College Location","mandatory":true,"options":""},{"name":"PG University Name","mandatory":true,"options":""},{"name":"Active Backlogs (PG)?","mandatory":true,"options":"Yes, No"},{"name":"No. of Backlogs (PG)","mandatory":true,"options":""},{"name":"Have Prior Full-time Experience?","mandatory":true,"options":"Yes, No"},{"name":"Company Name","mandatory":true,"options":""},{"name":"Designation","mandatory":true,"options":""},{"name":"Duration (Months)","mandatory":true,"options":""},{"name":"Job Role Description","mandatory":true,"options":""},{"name":"Last Drawn Salary (If any)","mandatory":true,"options":""},{"name":"Reason for Leaving (If any)","mandatory":true,"options":""},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","mandatory":true,"options":"I Agree"},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"},{"name":"Declaration of Authenticity","mandatory":true,"options":"I Agree"},{"name":"Agree to Terms and Conditions","mandatory":true,"options":"I Agree"}]</t>
-  </si>
-  <si>
-    <t>2026, 2027</t>
-  </si>
-  <si>
-    <t>Devnanda</t>
-  </si>
-  <si>
-    <t>Software engineer</t>
-  </si>
-  <si>
-    <t>["BSc-Biochemistry","BSc-Botany_Microbiology","BSc-Botany_Zoology","BSc-Chemistry_Biotechnology","BSc-Chemistry_Microbiology","BSc-COMPOSITE HOME SCIENCE","BSc-Computer Science_Mathematics","BSc-Economics_Statistics","BSc-Environmental Science &amp; Sustainability_Life Sciences","BSc-Mathematics_Physics","BSc-Microbiology_Zoology","BSc-Nutrition &amp; Dietetics_Human Development","BSc-Zoology_Biotechnology","BSc-Biotechnology","BSc-Data Science","BSc-Fashion and Apparel Design","BSc-Food Science &amp; Nutrition","BSc-Interior Design &amp; Management","Bachelor of Computer Applications","MSc-Biochemistry","MSc-Biotechnology","MSc-Botany","MSc-Chemistry","MSc-Computer Science (Data Science Specialization)","MSc-Electronics","MSc-Food Science &amp; Nutrition","MSc-Life Science","MSc-Mathematics","MSc-Psychology","MSc-Human Development","Master of Computer Applications"]</t>
-  </si>
-  <si>
-    <t>1000000</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>800000</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>PwC</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","type":"text","options":"","mandatory":"1"},{"name":"First Name","type":"text","options":"","mandatory":"1"},{"name":"Middle Name","type":"text","options":"","mandatory":"1"},{"name":"Last Name","type":"text","options":"","mandatory":"1"},{"name":"Phone No","type":"text","options":"","mandatory":"1"},{"name":"Alternate Phone No","type":"text","options":"","mandatory":"1"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"1"},{"name":"Alternate Email ID","type":"text","options":"","mandatory":"1"},{"name":"Gender","type":"text","options":"Male, Female, Other","mandatory":"1"},{"name":"DOB","type":"text","options":"","mandatory":"1"},{"name":"Hometown","type":"text","options":"","mandatory":"1"},{"name":"State","type":"text","options":"","mandatory":"1"},{"name":"District","type":"text","options":"","mandatory":"1"},{"name":"City (Currently Residing In)","type":"text","options":"","mandatory":"1"},{"name":"Pincode","type":"text","options":"","mandatory":"1"},{"name":"Current Address","type":"text","options":"","mandatory":"1"},{"name":"Permanent Address","type":"text","options":"","mandatory":"1"},{"name":"PAN No","type":"text","options":"","mandatory":"1"},{"name":"Aadhar No","type":"text","options":"","mandatory":"1"},{"name":"Passport No","type":"text","options":"","mandatory":"1"},{"name":"Nationality","type":"text","options":"","mandatory":"1"},{"name":"Category (General\/OBC\/SC\/ST)","type":"text","options":"General, OBC, SC, ST","mandatory":"1"},{"name":"Religion","type":"text","options":"Hindu, Christian, Muslim, Sikh, Jain, Other","mandatory":"1"},{"name":"Blood Group","type":"text","options":"A+, A-, B+, B-, AB+, AB-, O+, O-","mandatory":"1"},{"name":"Marital Status","type":"text","options":"Single, Married, Divorced, Widowed","mandatory":"1"},{"name":"Father\u2019s Name","type":"text","options":"","mandatory":"1"},{"name":"Mother\u2019s Name","type":"text","options":"","mandatory":"1"},{"name":"Emergency Contact Name","type":"text","options":"","mandatory":"1"},{"name":"Emergency Contact Number","type":"text","options":"","mandatory":"1"},{"name":"10th grade %","type":"text","options":"","mandatory":"1"},{"name":"10th Board Name","type":"text","options":"","mandatory":"1"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"10th School Name","type":"text","options":"","mandatory":"1"},{"name":"10th School Location","type":"text","options":"","mandatory":"1"},{"name":"UG Degree","type":"text","options":"","mandatory":"1"},{"name":"UG Course Name","type":"text","options":"","mandatory":"1"},{"name":"UG %\/CGPA","type":"text","options":"","mandatory":"1"},{"name":"UG Year of Passing","type":"text","options":"","mandatory":"1"},{"name":"UG Stream\/Specialization","type":"text","options":"","mandatory":"1"},{"name":"UG College Name","type":"text","options":"","mandatory":"1"},{"name":"UG College Location","type":"text","options":"","mandatory":"1"},{"name":"UG University Name","type":"text","options":"","mandatory":"1"},{"name":"Active Backlogs (UG)?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Backlogs (UG)","type":"text","options":"","mandatory":"1"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"1"},{"name":"12th Board Name","type":"text","options":"","mandatory":"1"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC School Name","type":"text","options":"","mandatory":"1"},{"name":"12th\/PUC Location","type":"text","options":"","mandatory":"1"},{"name":"12th Stream","type":"text","options":"","mandatory":"1"},{"name":"PG Degree","type":"text","options":"","mandatory":"1"},{"name":"PG Course Name","type":"text","options":"","mandatory":"1"},{"name":"PG %\/CGPA","type":"text","options":"","mandatory":"1"},{"name":"PG Year of Passing","type":"text","options":"","mandatory":"1"},{"name":"PG Stream\/Specialization","type":"text","options":"","mandatory":"1"},{"name":"PG College Name","type":"text","options":"","mandatory":"1"},{"name":"PG College Location","type":"text","options":"","mandatory":"1"},{"name":"PG University Name","type":"text","options":"","mandatory":"1"},{"name":"Active Backlogs (PG)?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Backlogs (PG)","type":"text","options":"","mandatory":"1"},{"name":"Have you completed any internship?","type":"text","options":"Yes, No","mandatory":"1"},{"name":"No. of Months of Internship","type":"text","options":"","mandatory":"1"},{"name":"Name of Organization","type":"text","options":"","mandatory":"1"},{"name":"Internship Role","type":"text","options":"","mandatory":"1"},{"name":"Internship Project Details","type":"text","options":"","mandatory":"1"},{"name":"Internship Location","type":"text","options":"","mandatory":"1"},{"name":"Certificate of Internship","type":"text","options":"","mandatory":"1"},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","type":"text","options":"I Agree","mandatory":"1"},{"name":"I hereby declare that the above information is correct.","type":"text","options":"I Agree","mandatory":"1"},{"name":"Declaration of Authenticity","type":"text","options":"I Agree","mandatory":"1"},{"name":"Agree to Terms and Conditions","type":"text","options":"I Agree","mandatory":"1"}]</t>
-  </si>
-  <si>
-    <t>2025, 2026, 2027, 2028</t>
-  </si>
-  <si>
-    <t>2028-2029</t>
-  </si>
-  <si>
-    <t>Manager</t>
-  </si>
-  <si>
-    <t>9:30AM-6:30PM</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>D E Shaw</t>
-  </si>
-  <si>
-    <t>Global investment &amp; Technology</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Alternate Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"Alternate Email ID","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Board Name","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Board Name","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"UG Degree","mandatory":true,"options":""},{"name":"UG Course Name","mandatory":true,"options":""},{"name":"UG %/CGPA","mandatory":true,"options":""},{"name":"UG Year of Passing","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"Certificate of Internship","mandatory":true,"options":""},{"name":"I hereby undertake that I will appear for the complete recruitment process of the above mentioned organization. In case I fail to appear for the same, my candidature for next companies stands cancelled. I also confirm that I have not been placed so far.","mandatory":true,"options":"I Agree"},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"},{"name":"Declaration of Authenticity","mandatory":true,"options":"I Agree"},{"name":"Agree to Terms and Conditions","mandatory":true,"options":"I Agree"}]</t>
-  </si>
-  <si>
-    <t>2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Intern </t>
-  </si>
-  <si>
-    <t>900000</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>9:00AM- 6:00 PM</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>[{"name":"Full Name","mandatory":true,"options":""},{"name":"Phone No","mandatory":true,"options":""},{"name":"Email ID (please recheck the email before submitting)","mandatory":true,"options":""},{"name":"10th grade %","mandatory":true,"options":""},{"name":"10th Year Of Passing","mandatory":true,"options":""},{"name":"12th grade/PUC %","mandatory":true,"options":""},{"name":"12th Year Of Passing","mandatory":true,"options":""},{"name":"Have you completed any internship?","mandatory":true,"options":"Yes, No"},{"name":"Name of Organization","mandatory":true,"options":""},{"name":"Internship Role","mandatory":true,"options":""},{"name":"I hereby declare that the above information is correct.","mandatory":true,"options":"I Agree"}]</t>
-  </si>
-  <si>
-    <t>madiha</t>
-  </si>
-  <si>
-    <t>Analyst Trainee</t>
-  </si>
-  <si>
-    <t>60,000</t>
-  </si>
-  <si>
-    <t>Apprenticeship (Part Time)</t>
+    <t>2026-05-03 12:00:00</t>
+  </si>
+  <si>
+    <t>[{"name":"Full Name","type":"text","options":"","mandatory":"1"},{"name":"Phone No","type":"text","options":"","mandatory":"1"},{"name":"Email ID (please recheck the email before submitting)","type":"text","options":"","mandatory":"1"},{"name":"10th grade %","type":"text","options":"","mandatory":"1"},{"name":"10th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"12th grade\/PUC %","type":"text","options":"","mandatory":"0"},{"name":"12th Year Of Passing","type":"text","options":"","mandatory":"1"},{"name":"UG Course Name","type":"text","options":"","mandatory":"0"},{"name":"UG %\/CGPA","type":"text","options":"","mandatory":"1"}]</t>
+  </si>
+  <si>
+    <t>Whitefield, Bangalore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation Analyst </t>
+  </si>
+  <si>
+    <t>["BCom-Business Process Services","BCom-Corporate Finance","BCom-General","BCom-Industry Integrated","BCom-International Accounting and Finance","BCom-Professional","BCom-Strategic Finance","BCom-Tourism and Travel Management","BA-Political Science_Economics","BA-Psychology_Economics","BA-Economics","BBA-Branding &amp; Advertising","BBA-Business Analytics","BBA-Regular","BSc-Economics_Statistics"]</t>
+  </si>
+  <si>
+    <t>90.00</t>
+  </si>
+  <si>
+    <t>10 LPA</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>UNSW</t>
+  </si>
+  <si>
+    <t>2026-05-04 21:49:28</t>
+  </si>
+  <si>
+    <t>Madiha S</t>
+  </si>
+  <si>
+    <t>analyst</t>
+  </si>
+  <si>
+    <t>["BBA-Regular"]</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>lvx</t>
+  </si>
+  <si>
+    <t>2026-05-04 22:08:40</t>
   </si>
   <si>
     <t>Placement_id</t>
   </si>
   <si>
+    <t>reg_no</t>
+  </si>
+  <si>
+    <t>course</t>
+  </si>
+  <si>
+    <t>percentage</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>applied_at</t>
+  </si>
+  <si>
+    <t>resume_file</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Phone No</t>
+  </si>
+  <si>
+    <t>Email ID (please recheck the email before submitting)</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>10th grade %</t>
+  </si>
+  <si>
+    <t>10th Year Of Passing</t>
+  </si>
+  <si>
+    <t>12th grade/PUC %</t>
+  </si>
+  <si>
+    <t>12th Year Of Passing</t>
+  </si>
+  <si>
+    <t>Resume</t>
+  </si>
+  <si>
+    <t>MCC26PLC679</t>
+  </si>
+  <si>
+    <t>MB24123</t>
+  </si>
+  <si>
+    <t>BBA-Regular</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>placed</t>
+  </si>
+  <si>
+    <t>2026-05-02 21:13:26</t>
+  </si>
+  <si>
+    <t>8296264517</t>
+  </si>
+  <si>
+    <t>madihasyeda1604@gmail.com</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>uploads/resumes/Madiha_Sresume69f61b9e0dace.pdf</t>
+  </si>
+  <si>
+    <t>MCC26INT18</t>
+  </si>
+  <si>
+    <t>MA241107</t>
+  </si>
+  <si>
+    <t>BA-Economics</t>
+  </si>
+  <si>
+    <t>blocked</t>
+  </si>
+  <si>
+    <t>2026-05-02 23:33:26</t>
+  </si>
+  <si>
+    <t>Abhijit</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>93.3</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>uploads/resumes/Abhijith_Manikantanresume69f63c6eb51c6.pdf</t>
+  </si>
+  <si>
     <t>program_type</t>
   </si>
   <si>
     <t>program</t>
   </si>
   <si>
-    <t>course</t>
-  </si>
-  <si>
-    <t>reg_no</t>
-  </si>
-  <si>
     <t>student_name</t>
   </si>
   <si>
@@ -778,162 +970,126 @@
     <t>9876543212</t>
   </si>
   <si>
-    <t>MCC26PLC679</t>
-  </si>
-  <si>
     <t>Bachelor of Business Administration</t>
   </si>
   <si>
-    <t>BBA - Finance</t>
-  </si>
-  <si>
-    <t>MB24123</t>
-  </si>
-  <si>
-    <t>Madiha S</t>
-  </si>
-  <si>
     <t>madihasyeda794@gmail.com</t>
   </si>
   <si>
     <t>$2y$10$DiUbSOJ0lfAM8w96Ui/gSOIMYUjRVWE4wCMrxJTiwZ5fIojPhZ66i</t>
   </si>
   <si>
-    <t>2026-05-01 22:12:12</t>
-  </si>
-  <si>
-    <t>8296264517</t>
+    <t>2026-05-05 01:45:59</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>MCC25VAN_TEST003</t>
+    <t>Bachelor of Arts</t>
+  </si>
+  <si>
+    <t>abhi@test.com</t>
+  </si>
+  <si>
+    <t>$2y$10$JLWShQCYsPIQtuhc7dei..S.ANSRVsbrG3uDxA1hgUYL5vSqyIHn.</t>
+  </si>
+  <si>
+    <t>2026-05-04 23:09:07</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>MCC25VAN_TEST005</t>
+  </si>
+  <si>
+    <t>Bachelor of Science</t>
+  </si>
+  <si>
+    <t>B.Sc - Computer Science</t>
+  </si>
+  <si>
+    <t>MB123460</t>
+  </si>
+  <si>
+    <t>Test Student 5</t>
+  </si>
+  <si>
+    <t>test5@example.com</t>
+  </si>
+  <si>
+    <t>9876543214</t>
+  </si>
+  <si>
+    <t>MCC25VAN_TEST006</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>Master of Business Administration</t>
+  </si>
+  <si>
+    <t>MBA - Marketing</t>
+  </si>
+  <si>
+    <t>MB223456</t>
+  </si>
+  <si>
+    <t>Test Student 6</t>
+  </si>
+  <si>
+    <t>test6@example.com</t>
+  </si>
+  <si>
+    <t>9876543215</t>
+  </si>
+  <si>
+    <t>MCC25VAN_TEST007</t>
+  </si>
+  <si>
+    <t>Master of Commerce</t>
+  </si>
+  <si>
+    <t>M.Com - Finance</t>
+  </si>
+  <si>
+    <t>MB223457</t>
+  </si>
+  <si>
+    <t>Test Student 7</t>
+  </si>
+  <si>
+    <t>test7@example.com</t>
+  </si>
+  <si>
+    <t>9876543216</t>
+  </si>
+  <si>
+    <t>MCC25VAN_TEST008</t>
+  </si>
+  <si>
+    <t>BBA - Marketing</t>
+  </si>
+  <si>
+    <t>MB123461</t>
+  </si>
+  <si>
+    <t>Test Student 8</t>
+  </si>
+  <si>
+    <t>test8@example.com</t>
+  </si>
+  <si>
+    <t>9876543217</t>
+  </si>
+  <si>
+    <t>MCC25VAN_TEST009</t>
   </si>
   <si>
     <t>Bachelor of Commerce</t>
   </si>
   <si>
-    <t>B.Com - Accounting</t>
-  </si>
-  <si>
-    <t>MB123458</t>
-  </si>
-  <si>
-    <t>Test Student 3</t>
-  </si>
-  <si>
-    <t>test3@example.com</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST004</t>
-  </si>
-  <si>
-    <t>Bachelor of Arts</t>
-  </si>
-  <si>
-    <t>BA - Psychology</t>
-  </si>
-  <si>
-    <t>MB123459</t>
-  </si>
-  <si>
-    <t>Test Student 4</t>
-  </si>
-  <si>
-    <t>test4@example.com</t>
-  </si>
-  <si>
-    <t>9876543213</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST005</t>
-  </si>
-  <si>
-    <t>Bachelor of Science</t>
-  </si>
-  <si>
-    <t>B.Sc - Computer Science</t>
-  </si>
-  <si>
-    <t>MB123460</t>
-  </si>
-  <si>
-    <t>Test Student 5</t>
-  </si>
-  <si>
-    <t>test5@example.com</t>
-  </si>
-  <si>
-    <t>9876543214</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST006</t>
-  </si>
-  <si>
-    <t>PG</t>
-  </si>
-  <si>
-    <t>Master of Business Administration</t>
-  </si>
-  <si>
-    <t>MBA - Marketing</t>
-  </si>
-  <si>
-    <t>MB223456</t>
-  </si>
-  <si>
-    <t>Test Student 6</t>
-  </si>
-  <si>
-    <t>test6@example.com</t>
-  </si>
-  <si>
-    <t>9876543215</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST007</t>
-  </si>
-  <si>
-    <t>Master of Commerce</t>
-  </si>
-  <si>
-    <t>M.Com - Finance</t>
-  </si>
-  <si>
-    <t>MB223457</t>
-  </si>
-  <si>
-    <t>Test Student 7</t>
-  </si>
-  <si>
-    <t>test7@example.com</t>
-  </si>
-  <si>
-    <t>9876543216</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST008</t>
-  </si>
-  <si>
-    <t>BBA - Marketing</t>
-  </si>
-  <si>
-    <t>MB123461</t>
-  </si>
-  <si>
-    <t>Test Student 8</t>
-  </si>
-  <si>
-    <t>test8@example.com</t>
-  </si>
-  <si>
-    <t>9876543217</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST009</t>
-  </si>
-  <si>
     <t>B.Com - Finance</t>
   </si>
   <si>
@@ -967,9 +1123,108 @@
     <t>9876543219</t>
   </si>
   <si>
+    <t>MCC26PLC18</t>
+  </si>
+  <si>
+    <t>noyes@mail.com</t>
+  </si>
+  <si>
+    <t>$2y$10$a/thOGsDQEUWQ2ZNHVmJSOxB4z64l6rB1g6yAF0bK0zu7R/KhOnfO</t>
+  </si>
+  <si>
+    <t>MCC26PLC678</t>
+  </si>
+  <si>
+    <t>MB24124</t>
+  </si>
+  <si>
+    <t>Khushi</t>
+  </si>
+  <si>
+    <t>khushi17</t>
+  </si>
+  <si>
+    <t>MCC26PLC697</t>
+  </si>
+  <si>
+    <t>MB24121</t>
+  </si>
+  <si>
+    <t>khilnani</t>
+  </si>
+  <si>
     <t>role</t>
   </si>
   <si>
+    <t>offer_letter_accepted</t>
+  </si>
+  <si>
+    <t>offer_letter_received</t>
+  </si>
+  <si>
+    <t>joining_status</t>
+  </si>
+  <si>
+    <t>filled_on_off_form</t>
+  </si>
+  <si>
+    <t>Application_type</t>
+  </si>
+  <si>
+    <t>not filled</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>course_name</t>
+  </si>
+  <si>
+    <t>intent_letter_received</t>
+  </si>
+  <si>
+    <t>onboarding_date</t>
+  </si>
+  <si>
+    <t>campus_type</t>
+  </si>
+  <si>
+    <t>photo_path</t>
+  </si>
+  <si>
+    <t>offer_letter_file</t>
+  </si>
+  <si>
+    <t>passing_year</t>
+  </si>
+  <si>
+    <t>intent_letter_file</t>
+  </si>
+  <si>
+    <t>register_type</t>
+  </si>
+  <si>
+    <t>JPMorgan Chase &amp; Co</t>
+  </si>
+  <si>
+    <t>Syeda Madiha Fathima</t>
+  </si>
+  <si>
+    <t>MB237256</t>
+  </si>
+  <si>
+    <t>BBA - Healthcare</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>uploads/Syeda_Madiha_Fathima_MB237256_JPMorgan_Chase___Co_photo.jpeg</t>
+  </si>
+  <si>
     <t>Form Open Date</t>
   </si>
   <si>
@@ -1009,15 +1264,30 @@
     <t>2026-04-30 23:39:11</t>
   </si>
   <si>
+    <t>2026-05-04 23:39:10</t>
+  </si>
+  <si>
+    <t>2026-05-05 17:00:00</t>
+  </si>
+  <si>
+    <t>2026-05-05 00:37:45</t>
+  </si>
+  <si>
     <t>2026-05-01 00:22:01</t>
   </si>
   <si>
-    <t>2026-05-05 17:00:00</t>
-  </si>
-  <si>
     <t>2026-05-01 17:00:00</t>
   </si>
   <si>
+    <t>Process complete</t>
+  </si>
+  <si>
+    <t>2026-05-02 20:12:01</t>
+  </si>
+  <si>
+    <t>2026-05-02 21:14:17</t>
+  </si>
+  <si>
     <t>2026-05-06 12:00:00</t>
   </si>
   <si>
@@ -1033,10 +1303,13 @@
     <t>2026-06-12 12:00:00</t>
   </si>
   <si>
-    <t>2026-05-03 12:00:00</t>
-  </si>
-  <si>
-    <t>2026-05-01 09:48:04</t>
+    <t>No applicants</t>
+  </si>
+  <si>
+    <t>2026-05-05 01:37:07</t>
+  </si>
+  <si>
+    <t>2026-05-03 02:22:42</t>
   </si>
   <si>
     <t>2026-05-02 11:00:00</t>
@@ -1058,6 +1331,15 @@
   </si>
   <si>
     <t>2026-05-02 00:42:37</t>
+  </si>
+  <si>
+    <t>2026-05-05 00:51:52</t>
+  </si>
+  <si>
+    <t>2026-05-05 01:25:30</t>
+  </si>
+  <si>
+    <t>2026-05-05 01:38:55</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1691,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -2008,23 +2290,23 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>83</v>
@@ -2039,7 +2321,7 @@
         <v>35</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>102</v>
@@ -2048,13 +2330,13 @@
         <v>38</v>
       </c>
       <c r="S9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
@@ -2063,27 +2345,27 @@
         <v>55</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:26" customHeight="1" ht="20">
       <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
@@ -2111,19 +2393,19 @@
         <v>35</v>
       </c>
       <c r="P10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="S10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>87</v>
@@ -2135,15 +2417,15 @@
         <v>55</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:26" customHeight="1" ht="20">
       <c r="A11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>28</v>
@@ -2153,11 +2435,11 @@
         <v>29</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>32</v>
@@ -2166,7 +2448,7 @@
         <v>62</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>83</v>
@@ -2181,20 +2463,20 @@
         <v>35</v>
       </c>
       <c r="P11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
@@ -2208,33 +2490,33 @@
     </row>
     <row r="12" spans="1:26" customHeight="1" ht="20">
       <c r="A12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
@@ -2249,10 +2531,10 @@
         <v>35</v>
       </c>
       <c r="P12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q12" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
@@ -2260,7 +2542,7 @@
         <v>103</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
@@ -2274,24 +2556,24 @@
     </row>
     <row r="13" spans="1:26" customHeight="1" ht="20">
       <c r="A13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>148</v>
@@ -2300,7 +2582,7 @@
         <v>149</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
@@ -2323,7 +2605,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U13" s="2" t="s">
         <v>152</v>
@@ -2335,7 +2617,7 @@
         <v>105</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:26" customHeight="1" ht="20">
@@ -2357,9 +2639,11 @@
       <c r="F14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>157</v>
+      </c>
       <c r="H14" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>148</v>
@@ -2368,7 +2652,7 @@
         <v>62</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>26</v>
@@ -2383,33 +2667,35 @@
         <v>35</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
+      <c r="Y14" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="Z14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:26" customHeight="1" ht="20">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>43</v>
@@ -2419,11 +2705,11 @@
         <v>29</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>48</v>
@@ -2432,7 +2718,7 @@
         <v>62</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
@@ -2447,20 +2733,20 @@
         <v>50</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>38</v>
       </c>
       <c r="S15" s="2"/>
       <c r="T15" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -2469,18 +2755,18 @@
         <v>105</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:26" customHeight="1" ht="20">
       <c r="A16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
@@ -2491,14 +2777,14 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
@@ -2513,14 +2799,14 @@
         <v>35</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R16" s="2"/>
       <c r="S16" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
@@ -2531,18 +2817,18 @@
         <v>66</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:26" customHeight="1" ht="20">
       <c r="A17" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
@@ -2553,14 +2839,14 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -2578,11 +2864,11 @@
         <v>73</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R17" s="2"/>
       <c r="S17" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
@@ -2593,15 +2879,15 @@
         <v>66</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:26" customHeight="1" ht="20">
       <c r="A18" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -2615,14 +2901,14 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>83</v>
@@ -2634,21 +2920,21 @@
         <v>26</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
@@ -2662,33 +2948,33 @@
     </row>
     <row r="19" spans="1:26" customHeight="1" ht="20">
       <c r="A19" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>26</v>
@@ -2703,7 +2989,7 @@
         <v>50</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>85</v>
@@ -2712,13 +2998,13 @@
         <v>38</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
@@ -2727,15 +3013,15 @@
         <v>42</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:26" customHeight="1" ht="20">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>28</v>
@@ -2749,14 +3035,14 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
@@ -2768,27 +3054,267 @@
         <v>83</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z20" s="2"/>
+    </row>
+    <row r="21" spans="1:26" customHeight="1" ht="20">
+      <c r="A21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" customHeight="1" ht="20">
+      <c r="A22" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" customHeight="1" ht="20">
+      <c r="A23" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z23" s="2"/>
+    </row>
+    <row r="24" spans="1:26" customHeight="1" ht="20">
+      <c r="A24" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z24" s="2"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -2811,9 +3337,214 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30" customWidth="true" style="0"/>
+    <col min="3" max="3" width="30" customWidth="true" style="0"/>
+    <col min="4" max="4" width="30" customWidth="true" style="0"/>
+    <col min="5" max="5" width="30" customWidth="true" style="0"/>
+    <col min="6" max="6" width="30" customWidth="true" style="0"/>
+    <col min="7" max="7" width="30" customWidth="true" style="0"/>
+    <col min="8" max="8" width="30" customWidth="true" style="0"/>
+    <col min="9" max="9" width="30" customWidth="true" style="0"/>
+    <col min="10" max="10" width="30" customWidth="true" style="0"/>
+    <col min="11" max="11" width="30" customWidth="true" style="0"/>
+    <col min="12" max="12" width="30" customWidth="true" style="0"/>
+    <col min="13" max="13" width="30" customWidth="true" style="0"/>
+    <col min="14" max="14" width="30" customWidth="true" style="0"/>
+    <col min="15" max="15" width="30" customWidth="true" style="0"/>
+    <col min="16" max="16" width="30" customWidth="true" style="0"/>
+    <col min="17" max="17" width="30" customWidth="true" style="0"/>
+    <col min="18" max="18" width="30" customWidth="true" style="0"/>
+    <col min="19" max="19" width="30" customWidth="true" style="0"/>
+    <col min="20" max="20" width="30" customWidth="true" style="0"/>
+    <col min="21" max="21" width="30" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" customHeight="1" ht="20">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" customHeight="1" ht="20">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -2834,7 +3565,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -2870,52 +3601,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>215</v>
+        <v>279</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>220</v>
+        <v>284</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>221</v>
+        <v>285</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>1</v>
@@ -2924,25 +3655,25 @@
         <v>24</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:26" customHeight="1" ht="20">
@@ -2950,25 +3681,25 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
@@ -2979,16 +3710,16 @@
         <v>83</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -3000,16 +3731,16 @@
         <v>35</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z2" s="2"/>
     </row>
@@ -3018,25 +3749,25 @@
         <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
@@ -3047,16 +3778,16 @@
         <v>83</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>246</v>
+        <v>310</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -3068,16 +3799,16 @@
         <v>35</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z3" s="2"/>
     </row>
@@ -3086,25 +3817,25 @@
         <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>248</v>
+        <v>312</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
@@ -3115,16 +3846,16 @@
         <v>83</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -3136,16 +3867,16 @@
         <v>35</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z4" s="2"/>
     </row>
@@ -3154,53 +3885,57 @@
         <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>258</v>
+        <v>318</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="T5" s="2" t="s">
         <v>48</v>
       </c>
@@ -3208,16 +3943,16 @@
         <v>35</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z5" s="2"/>
     </row>
@@ -3226,49 +3961,57 @@
         <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>263</v>
+        <v>321</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>266</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I6" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>323</v>
+      </c>
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>324</v>
+      </c>
       <c r="L6" s="2" t="s">
         <v>83</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="R6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="T6" s="2" t="s">
         <v>48</v>
       </c>
@@ -3276,16 +4019,16 @@
         <v>35</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z6" s="2"/>
     </row>
@@ -3294,25 +4037,25 @@
         <v>88</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>270</v>
+        <v>328</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>271</v>
+        <v>329</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>272</v>
+        <v>330</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
@@ -3323,16 +4066,16 @@
         <v>83</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>274</v>
+        <v>332</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -3344,16 +4087,16 @@
         <v>35</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z7" s="2"/>
     </row>
@@ -3362,25 +4105,25 @@
         <v>96</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>229</v>
+        <v>334</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>277</v>
+        <v>336</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
@@ -3391,16 +4134,16 @@
         <v>83</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -3412,16 +4155,16 @@
         <v>35</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z8" s="2"/>
     </row>
@@ -3430,25 +4173,25 @@
         <v>106</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>284</v>
+        <v>342</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>285</v>
+        <v>343</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>286</v>
+        <v>344</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>288</v>
+        <v>346</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
@@ -3459,16 +4202,16 @@
         <v>83</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>289</v>
+        <v>347</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -3480,43 +4223,43 @@
         <v>35</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" customHeight="1" ht="20">
       <c r="A10" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>293</v>
+        <v>350</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>294</v>
+        <v>351</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>295</v>
+        <v>352</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
@@ -3527,16 +4270,16 @@
         <v>83</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>296</v>
+        <v>353</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -3548,43 +4291,43 @@
         <v>35</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" customHeight="1" ht="20">
       <c r="A11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>301</v>
+        <v>359</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
@@ -3595,16 +4338,16 @@
         <v>83</v>
       </c>
       <c r="M11" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -3616,43 +4359,43 @@
         <v>35</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" customHeight="1" ht="20">
       <c r="A12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
@@ -3663,16 +4406,16 @@
         <v>83</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -3684,45 +4427,47 @@
         <v>35</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" customHeight="1" ht="20">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>309</v>
+        <v>367</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>253</v>
+        <v>321</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>312</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="I13" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>369</v>
+      </c>
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
@@ -3731,16 +4476,16 @@
         <v>83</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>236</v>
+        <v>35</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -3749,21 +4494,153 @@
         <v>48</v>
       </c>
       <c r="U13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" spans="1:26" customHeight="1" ht="20">
+      <c r="A14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V13" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z13" s="2"/>
+      <c r="V14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" spans="1:26" customHeight="1" ht="20">
+      <c r="A15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Z15" s="2"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -3786,9 +4663,268 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30" customWidth="true" style="0"/>
+    <col min="3" max="3" width="30" customWidth="true" style="0"/>
+    <col min="4" max="4" width="30" customWidth="true" style="0"/>
+    <col min="5" max="5" width="30" customWidth="true" style="0"/>
+    <col min="6" max="6" width="30" customWidth="true" style="0"/>
+    <col min="7" max="7" width="30" customWidth="true" style="0"/>
+    <col min="8" max="8" width="30" customWidth="true" style="0"/>
+    <col min="9" max="9" width="30" customWidth="true" style="0"/>
+    <col min="10" max="10" width="30" customWidth="true" style="0"/>
+    <col min="11" max="11" width="30" customWidth="true" style="0"/>
+    <col min="12" max="12" width="30" customWidth="true" style="0"/>
+    <col min="13" max="13" width="30" customWidth="true" style="0"/>
+    <col min="14" max="14" width="30" customWidth="true" style="0"/>
+    <col min="15" max="15" width="30" customWidth="true" style="0"/>
+    <col min="16" max="16" width="30" customWidth="true" style="0"/>
+    <col min="17" max="17" width="30" customWidth="true" style="0"/>
+    <col min="18" max="18" width="30" customWidth="true" style="0"/>
+    <col min="19" max="19" width="30" customWidth="true" style="0"/>
+    <col min="20" max="20" width="30" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" customHeight="1" ht="20">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" customHeight="1" ht="20">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" customHeight="1" ht="20">
+      <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -3809,9 +4945,137 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30" customWidth="true" style="0"/>
+    <col min="3" max="3" width="30" customWidth="true" style="0"/>
+    <col min="4" max="4" width="30" customWidth="true" style="0"/>
+    <col min="5" max="5" width="30" customWidth="true" style="0"/>
+    <col min="6" max="6" width="30" customWidth="true" style="0"/>
+    <col min="7" max="7" width="30" customWidth="true" style="0"/>
+    <col min="8" max="8" width="30" customWidth="true" style="0"/>
+    <col min="9" max="9" width="30" customWidth="true" style="0"/>
+    <col min="10" max="10" width="30" customWidth="true" style="0"/>
+    <col min="11" max="11" width="30" customWidth="true" style="0"/>
+    <col min="12" max="12" width="30" customWidth="true" style="0"/>
+    <col min="13" max="13" width="30" customWidth="true" style="0"/>
+    <col min="14" max="14" width="30" customWidth="true" style="0"/>
+    <col min="15" max="15" width="30" customWidth="true" style="0"/>
+    <col min="16" max="16" width="30" customWidth="true" style="0"/>
+    <col min="17" max="17" width="30" customWidth="true" style="0"/>
+    <col min="18" max="18" width="30" customWidth="true" style="0"/>
+    <col min="19" max="19" width="30" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" customHeight="1" ht="20">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+    </row>
+  </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -3832,7 +5096,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="true" style="0"/>
@@ -3865,7 +5129,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>10</v>
@@ -3880,31 +5144,31 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>316</v>
+        <v>401</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>317</v>
+        <v>402</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>318</v>
+        <v>403</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>319</v>
+        <v>404</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>320</v>
+        <v>405</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>323</v>
+        <v>408</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>324</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:17" customHeight="1" ht="20">
@@ -3936,7 +5200,7 @@
         <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -3947,7 +5211,7 @@
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>326</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:17" customHeight="1" ht="20">
@@ -3979,7 +5243,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>327</v>
+        <v>412</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -3988,7 +5252,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>328</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:17" customHeight="1" ht="20">
@@ -4020,7 +5284,7 @@
         <v>59</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -4031,7 +5295,7 @@
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>329</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:17" customHeight="1" ht="20">
@@ -4063,7 +5327,7 @@
         <v>71</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>330</v>
+        <v>415</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -4074,7 +5338,7 @@
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>329</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:17" customHeight="1" ht="20">
@@ -4106,7 +5370,7 @@
         <v>59</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -4117,7 +5381,7 @@
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>329</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:17" customHeight="1" ht="20">
@@ -4149,18 +5413,20 @@
         <v>59</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>331</v>
+        <v>418</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="N7" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="O7" s="2" t="s">
         <v>83</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>329</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:17" customHeight="1" ht="20">
@@ -4192,7 +5458,7 @@
         <v>99</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -4203,7 +5469,7 @@
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>326</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:17" customHeight="1" ht="20">
@@ -4214,19 +5480,19 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>102</v>
@@ -4235,7 +5501,7 @@
         <v>99</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>327</v>
+        <v>412</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -4246,21 +5512,21 @@
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>329</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:17" customHeight="1" ht="20">
       <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>82</v>
@@ -4269,16 +5535,16 @@
         <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>332</v>
+        <v>422</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -4289,24 +5555,24 @@
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2" t="s">
-        <v>329</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:17" customHeight="1" ht="20">
       <c r="A11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>66</v>
@@ -4315,13 +5581,13 @@
         <v>28</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>332</v>
+        <v>422</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -4332,24 +5598,24 @@
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>333</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:17" customHeight="1" ht="20">
       <c r="A12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>105</v>
@@ -4358,13 +5624,13 @@
         <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -4375,15 +5641,15 @@
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>335</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:17" customHeight="1" ht="20">
       <c r="A13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>29</v>
@@ -4392,33 +5658,35 @@
         <v>150</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>105</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>427</v>
+      </c>
       <c r="O13" s="2" t="s">
         <v>83</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:17" customHeight="1" ht="20">
@@ -4432,64 +5700,68 @@
         <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>337</v>
+        <v>216</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>338</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:17" customHeight="1" ht="20">
       <c r="A15" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>105</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>339</v>
+        <v>430</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -4498,39 +5770,39 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>340</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:17" customHeight="1" ht="20">
       <c r="A16" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>99</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -4541,15 +5813,15 @@
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
-        <v>341</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" spans="1:17" customHeight="1" ht="20">
       <c r="A17" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>29</v>
@@ -4558,22 +5830,22 @@
         <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>99</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -4584,24 +5856,24 @@
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>341</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:17" customHeight="1" ht="20">
       <c r="A18" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>66</v>
@@ -4610,13 +5882,13 @@
         <v>67</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>99</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>342</v>
+        <v>433</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -4627,39 +5899,39 @@
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>343</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:17" customHeight="1" ht="20">
       <c r="A19" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>339</v>
+        <v>430</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -4668,37 +5940,37 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>344</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:17" customHeight="1" ht="20">
       <c r="A20" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>99</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>327</v>
+        <v>412</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -4709,7 +5981,177 @@
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2" t="s">
-        <v>345</v>
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" customHeight="1" ht="20">
+      <c r="A21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" customHeight="1" ht="20">
+      <c r="A22" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" customHeight="1" ht="20">
+      <c r="A23" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" customHeight="1" ht="20">
+      <c r="A24" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/backups/DATA/2026/05/placement_backup_latest.xlsx
+++ b/backups/DATA/2026/05/placement_backup_latest.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="441">
   <si>
     <t>Sl No</t>
   </si>
@@ -820,205 +820,208 @@
     <t>BA-Economics</t>
   </si>
   <si>
+    <t>not_placed</t>
+  </si>
+  <si>
+    <t>2026-05-02 23:33:26</t>
+  </si>
+  <si>
+    <t>Abhijit</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>93.3</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>uploads/resumes/Abhijith_Manikantanresume69f63c6eb51c6.pdf</t>
+  </si>
+  <si>
+    <t>program_type</t>
+  </si>
+  <si>
+    <t>program</t>
+  </si>
+  <si>
+    <t>student_name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password_hash</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>last_login</t>
+  </si>
+  <si>
+    <t>email_verified</t>
+  </si>
+  <si>
+    <t>phone_no</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>placed_status</t>
+  </si>
+  <si>
+    <t>allow_reapply</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>year_of_passing</t>
+  </si>
+  <si>
+    <t>vantage_participant</t>
+  </si>
+  <si>
+    <t>vantage_placed</t>
+  </si>
+  <si>
+    <t>placement_category</t>
+  </si>
+  <si>
+    <t>Offcampus_selection</t>
+  </si>
+  <si>
+    <t>editable_comment</t>
+  </si>
+  <si>
+    <t>UP001</t>
+  </si>
+  <si>
+    <t>UG</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Computer Science</t>
+  </si>
+  <si>
+    <t>REG2024001</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>john.doe@example.com</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>2024-2027</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>UP002</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>REG2024002</t>
+  </si>
+  <si>
+    <t>Jane Smith</t>
+  </si>
+  <si>
+    <t>jane.smith@example.com</t>
+  </si>
+  <si>
+    <t>9876543211</t>
+  </si>
+  <si>
+    <t>UP003</t>
+  </si>
+  <si>
+    <t>REG2024003</t>
+  </si>
+  <si>
+    <t>Bob Johnson</t>
+  </si>
+  <si>
+    <t>bob.johnson@example.com</t>
+  </si>
+  <si>
+    <t>9876543212</t>
+  </si>
+  <si>
+    <t>Bachelor of Business Administration</t>
+  </si>
+  <si>
+    <t>madihasyeda794@gmail.com</t>
+  </si>
+  <si>
+    <t>$2y$10$DiUbSOJ0lfAM8w96Ui/gSOIMYUjRVWE4wCMrxJTiwZ5fIojPhZ66i</t>
+  </si>
+  <si>
+    <t>2026-05-05 12:22:32</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Bachelor of Arts</t>
+  </si>
+  <si>
+    <t>abhi@test.com</t>
+  </si>
+  <si>
+    <t>$2y$10$JLWShQCYsPIQtuhc7dei..S.ANSRVsbrG3uDxA1hgUYL5vSqyIHn.</t>
+  </si>
+  <si>
+    <t>2026-05-05 12:24:25</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>MCC25VAN_TEST005</t>
+  </si>
+  <si>
+    <t>Bachelor of Science</t>
+  </si>
+  <si>
+    <t>B.Sc - Computer Science</t>
+  </si>
+  <si>
+    <t>MB123460</t>
+  </si>
+  <si>
+    <t>Test Student 5</t>
+  </si>
+  <si>
+    <t>test5@example.com</t>
+  </si>
+  <si>
+    <t>9876543214</t>
+  </si>
+  <si>
     <t>blocked</t>
   </si>
   <si>
-    <t>2026-05-02 23:33:26</t>
-  </si>
-  <si>
-    <t>Abhijit</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>93.3</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>uploads/resumes/Abhijith_Manikantanresume69f63c6eb51c6.pdf</t>
-  </si>
-  <si>
-    <t>program_type</t>
-  </si>
-  <si>
-    <t>program</t>
-  </si>
-  <si>
-    <t>student_name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password_hash</t>
-  </si>
-  <si>
-    <t>is_active</t>
-  </si>
-  <si>
-    <t>last_login</t>
-  </si>
-  <si>
-    <t>email_verified</t>
-  </si>
-  <si>
-    <t>phone_no</t>
-  </si>
-  <si>
-    <t>batch</t>
-  </si>
-  <si>
-    <t>placed_status</t>
-  </si>
-  <si>
-    <t>allow_reapply</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>year_of_passing</t>
-  </si>
-  <si>
-    <t>vantage_participant</t>
-  </si>
-  <si>
-    <t>vantage_placed</t>
-  </si>
-  <si>
-    <t>placement_category</t>
-  </si>
-  <si>
-    <t>Offcampus_selection</t>
-  </si>
-  <si>
-    <t>editable_comment</t>
-  </si>
-  <si>
-    <t>UP001</t>
-  </si>
-  <si>
-    <t>UG</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
-    <t>REG2024001</t>
-  </si>
-  <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>john.doe@example.com</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
-    <t>2024-2027</t>
-  </si>
-  <si>
-    <t>not_placed</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>UP002</t>
-  </si>
-  <si>
-    <t>Information Technology</t>
-  </si>
-  <si>
-    <t>REG2024002</t>
-  </si>
-  <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
-    <t>jane.smith@example.com</t>
-  </si>
-  <si>
-    <t>9876543211</t>
-  </si>
-  <si>
-    <t>UP003</t>
-  </si>
-  <si>
-    <t>REG2024003</t>
-  </si>
-  <si>
-    <t>Bob Johnson</t>
-  </si>
-  <si>
-    <t>bob.johnson@example.com</t>
-  </si>
-  <si>
-    <t>9876543212</t>
-  </si>
-  <si>
-    <t>Bachelor of Business Administration</t>
-  </si>
-  <si>
-    <t>madihasyeda794@gmail.com</t>
-  </si>
-  <si>
-    <t>$2y$10$DiUbSOJ0lfAM8w96Ui/gSOIMYUjRVWE4wCMrxJTiwZ5fIojPhZ66i</t>
-  </si>
-  <si>
-    <t>2026-05-05 01:45:59</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Bachelor of Arts</t>
-  </si>
-  <si>
-    <t>abhi@test.com</t>
-  </si>
-  <si>
-    <t>$2y$10$JLWShQCYsPIQtuhc7dei..S.ANSRVsbrG3uDxA1hgUYL5vSqyIHn.</t>
-  </si>
-  <si>
-    <t>2026-05-04 23:09:07</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
-    <t>MCC25VAN_TEST005</t>
-  </si>
-  <si>
-    <t>Bachelor of Science</t>
-  </si>
-  <si>
-    <t>B.Sc - Computer Science</t>
-  </si>
-  <si>
-    <t>MB123460</t>
-  </si>
-  <si>
-    <t>Test Student 5</t>
-  </si>
-  <si>
-    <t>test5@example.com</t>
-  </si>
-  <si>
-    <t>9876543214</t>
+    <t>Blocked by admin</t>
   </si>
   <si>
     <t>MCC25VAN_TEST006</t>
@@ -3164,7 +3167,7 @@
         <v>217</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>218</v>
@@ -3716,10 +3719,10 @@
         <v>300</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -3731,16 +3734,16 @@
         <v>35</v>
       </c>
       <c r="V2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="W2" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z2" s="2"/>
     </row>
@@ -3749,7 +3752,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>293</v>
@@ -3758,16 +3761,16 @@
         <v>294</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
@@ -3778,16 +3781,16 @@
         <v>83</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -3799,16 +3802,16 @@
         <v>35</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z3" s="2"/>
     </row>
@@ -3817,7 +3820,7 @@
         <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>293</v>
@@ -3829,13 +3832,13 @@
         <v>98</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
@@ -3846,16 +3849,16 @@
         <v>83</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O4" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -3867,16 +3870,16 @@
         <v>35</v>
       </c>
       <c r="V4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X4" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="W4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z4" s="2"/>
     </row>
@@ -3891,7 +3894,7 @@
         <v>293</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>253</v>
@@ -3903,16 +3906,16 @@
         <v>226</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>83</v>
@@ -3927,7 +3930,7 @@
         <v>255</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="2" t="s">
@@ -3943,16 +3946,16 @@
         <v>35</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z5" s="2"/>
     </row>
@@ -3967,7 +3970,7 @@
         <v>293</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>265</v>
@@ -3979,22 +3982,22 @@
         <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>83</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>300</v>
@@ -4003,15 +4006,11 @@
         <v>266</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
         <v>48</v>
       </c>
@@ -4019,16 +4018,16 @@
         <v>35</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W6" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X6" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z6" s="2"/>
     </row>
@@ -4037,25 +4036,25 @@
         <v>88</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
@@ -4066,18 +4065,20 @@
         <v>83</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O7" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q7" s="2"/>
+      <c r="Q7" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
@@ -4087,16 +4088,16 @@
         <v>35</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X7" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z7" s="2"/>
     </row>
@@ -4105,25 +4106,25 @@
         <v>96</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
@@ -4134,16 +4135,16 @@
         <v>83</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -4155,16 +4156,16 @@
         <v>35</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X8" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z8" s="2"/>
     </row>
@@ -4173,25 +4174,25 @@
         <v>106</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
@@ -4202,16 +4203,16 @@
         <v>83</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -4223,16 +4224,16 @@
         <v>35</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z9" s="2"/>
     </row>
@@ -4241,25 +4242,25 @@
         <v>116</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
@@ -4270,16 +4271,16 @@
         <v>83</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O10" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -4291,16 +4292,16 @@
         <v>35</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W10" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X10" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z10" s="2"/>
     </row>
@@ -4309,25 +4310,25 @@
         <v>126</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
@@ -4338,16 +4339,16 @@
         <v>83</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -4359,16 +4360,16 @@
         <v>35</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W11" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z11" s="2"/>
     </row>
@@ -4377,25 +4378,25 @@
         <v>134</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
@@ -4406,16 +4407,16 @@
         <v>83</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>300</v>
       </c>
       <c r="O12" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -4427,16 +4428,16 @@
         <v>35</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="W12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X12" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z12" s="2"/>
     </row>
@@ -4445,13 +4446,13 @@
         <v>144</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>265</v>
@@ -4463,10 +4464,10 @@
         <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>26</v>
@@ -4476,16 +4477,16 @@
         <v>83</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="O13" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -4497,16 +4498,16 @@
         <v>50</v>
       </c>
       <c r="V13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X13" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="W13" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X13" s="2" t="s">
+      <c r="Y13" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z13" s="2"/>
     </row>
@@ -4515,25 +4516,25 @@
         <v>153</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>253</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
@@ -4548,10 +4549,10 @@
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P14" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -4563,16 +4564,16 @@
         <v>35</v>
       </c>
       <c r="V14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X14" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="W14" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X14" s="2" t="s">
+      <c r="Y14" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z14" s="2"/>
     </row>
@@ -4581,25 +4582,25 @@
         <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>253</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
@@ -4614,10 +4615,10 @@
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -4629,16 +4630,16 @@
         <v>35</v>
       </c>
       <c r="V15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="X15" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="W15" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="X15" s="2" t="s">
+      <c r="Y15" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="Z15" s="2"/>
     </row>
@@ -4723,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>18</v>
@@ -4732,22 +4733,22 @@
         <v>19</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>285</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:20" customHeight="1" ht="20">
@@ -4755,25 +4756,25 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>253</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>257</v>
@@ -4792,20 +4793,20 @@
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:20" customHeight="1" ht="20">
@@ -4819,7 +4820,7 @@
         <v>293</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>253</v>
@@ -4831,7 +4832,7 @@
         <v>226</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>257</v>
@@ -4850,20 +4851,20 @@
         <v>161</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:20" customHeight="1" ht="20">
@@ -4871,25 +4872,25 @@
         <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>253</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>257</v>
@@ -4908,20 +4909,20 @@
         <v>213</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4977,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>234</v>
@@ -4989,43 +4990,43 @@
         <v>276</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>239</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:19" customHeight="1" ht="20">
@@ -5033,13 +5034,13 @@
         <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
@@ -5049,23 +5050,23 @@
         <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>257</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -5129,7 +5130,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>10</v>
@@ -5144,31 +5145,31 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:17" customHeight="1" ht="20">
@@ -5200,7 +5201,7 @@
         <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -5211,7 +5212,7 @@
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:17" customHeight="1" ht="20">
@@ -5243,7 +5244,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -5252,7 +5253,7 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:17" customHeight="1" ht="20">
@@ -5295,7 +5296,7 @@
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:17" customHeight="1" ht="20">
@@ -5327,7 +5328,7 @@
         <v>71</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -5338,7 +5339,7 @@
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:17" customHeight="1" ht="20">
@@ -5381,7 +5382,7 @@
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:17" customHeight="1" ht="20">
@@ -5413,20 +5414,20 @@
         <v>59</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>83</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:17" customHeight="1" ht="20">
@@ -5469,7 +5470,7 @@
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:17" customHeight="1" ht="20">
@@ -5501,7 +5502,7 @@
         <v>99</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -5512,7 +5513,7 @@
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:17" customHeight="1" ht="20">
@@ -5544,7 +5545,7 @@
         <v>120</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -5555,7 +5556,7 @@
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:17" customHeight="1" ht="20">
@@ -5587,7 +5588,7 @@
         <v>128</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -5598,7 +5599,7 @@
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:17" customHeight="1" ht="20">
@@ -5630,7 +5631,7 @@
         <v>137</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -5641,7 +5642,7 @@
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:17" customHeight="1" ht="20">
@@ -5673,20 +5674,20 @@
         <v>146</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>83</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:17" customHeight="1" ht="20">
@@ -5729,7 +5730,7 @@
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:17" customHeight="1" ht="20">
@@ -5761,7 +5762,7 @@
         <v>166</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -5770,7 +5771,7 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16" spans="1:17" customHeight="1" ht="20">
@@ -5813,7 +5814,7 @@
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:17" customHeight="1" ht="20">
@@ -5856,7 +5857,7 @@
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:17" customHeight="1" ht="20">
@@ -5888,7 +5889,7 @@
         <v>99</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -5899,7 +5900,7 @@
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:17" customHeight="1" ht="20">
@@ -5931,7 +5932,7 @@
         <v>166</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -5940,7 +5941,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:17" customHeight="1" ht="20">
@@ -5970,7 +5971,7 @@
         <v>99</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -5981,7 +5982,7 @@
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:17" customHeight="1" ht="20">
@@ -6024,7 +6025,7 @@
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:17" customHeight="1" ht="20">
@@ -6056,7 +6057,7 @@
         <v>216</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -6067,7 +6068,7 @@
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:17" customHeight="1" ht="20">
@@ -6103,14 +6104,14 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:17" customHeight="1" ht="20">
@@ -6151,7 +6152,7 @@
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
